--- a/target/PortalWeb-1.0-SNAPSHOT/resources/plano/estructura.xlsx
+++ b/target/PortalWeb-1.0-SNAPSHOT/resources/plano/estructura.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="13035"/>
+    <workbookView windowWidth="28800" windowHeight="12510"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -14,17 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>CÓDIGO ÍTEM:</t>
     </r>
     <r>
@@ -47,7 +39,7 @@
         <charset val="0"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Este es el código del ítem, debes utilizar tus propios códigos.</t>
+      <t>Este es el código del ítem que utilizas para cargar el pedido</t>
     </r>
   </si>
   <si>
@@ -74,7 +66,7 @@
         <charset val="0"/>
         <scheme val="minor"/>
       </rPr>
-      <t>si el ítem esta catalogado en unidades</t>
+      <t>si el ítem esta catalogado en unidades o metros</t>
     </r>
     <r>
       <rPr>
@@ -85,63 +77,22 @@
         <charset val="0"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.
-Números decimales:</t>
+      <t xml:space="preserve">.
+</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Si el ítem esta catalogado en metros , el formato es el siguiente 0.00</t>
-    </r>
-  </si>
-  <si>
-    <t>ITEM-1</t>
-  </si>
-  <si>
-    <t>ITEM-2</t>
-  </si>
-  <si>
-    <t>ITEM-3</t>
-  </si>
-  <si>
-    <t>ITEM-4</t>
-  </si>
-  <si>
-    <t>ITEM-5</t>
-  </si>
-  <si>
-    <t>ITEM-6</t>
-  </si>
-  <si>
-    <t>ITEM-7</t>
-  </si>
-  <si>
-    <t>ITEM-8</t>
-  </si>
-  <si>
-    <t>ITEM-9</t>
-  </si>
-  <si>
-    <t>ITEM-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="#,000_);[Red]\(#,000\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,16 +109,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,9 +185,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,22 +200,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -221,68 +239,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,13 +274,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,169 +442,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,6 +479,45 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,26 +546,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -593,201 +580,168 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1108,100 +1062,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.2857142857143" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.2857142857143" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="99" customHeight="1" spans="1:2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
+    <row r="7" spans="11:12">
+      <c r="K7" s="3"/>
+      <c r="L7" s="1"/>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
+    <row r="8" spans="11:12">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
+    <row r="9" spans="11:12">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
+    <row r="10" spans="11:12">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
+    <row r="11" spans="11:12">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
-        <v>7</v>
-      </c>
+    <row r="12" spans="11:12">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
-        <v>10</v>
-      </c>
+    <row r="13" spans="11:12">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
